--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N103_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N103_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.8911534165379</v>
+        <v>8.107312430187408</v>
       </c>
       <c r="D2" t="n">
-        <v>49.18312084022491</v>
+        <v>7.992257136536548</v>
       </c>
       <c r="E2" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F2" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.45267178863457</v>
+        <v>8.036059165653118</v>
       </c>
       <c r="D3" t="n">
-        <v>48.91730606055695</v>
+        <v>7.949062234840504</v>
       </c>
       <c r="E3" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F3" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.12870220806116</v>
+        <v>6.033414108809938</v>
       </c>
       <c r="D4" t="n">
-        <v>36.33926480856164</v>
+        <v>5.905130531391266</v>
       </c>
       <c r="E4" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F4" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.35790238780753</v>
+        <v>6.395659138018725</v>
       </c>
       <c r="D5" t="n">
-        <v>38.56097123848336</v>
+        <v>6.266157826253546</v>
       </c>
       <c r="E5" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F5" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.49552847891493</v>
+        <v>6.418023377823677</v>
       </c>
       <c r="D6" t="n">
-        <v>39.53233414302513</v>
+        <v>6.424004298241584</v>
       </c>
       <c r="E6" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F6" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.99094433112516</v>
+        <v>5.198528453807839</v>
       </c>
       <c r="D7" t="n">
-        <v>31.53911462939255</v>
+        <v>5.125106127276291</v>
       </c>
       <c r="E7" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F7" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.46721945775654</v>
+        <v>6.413423161885438</v>
       </c>
       <c r="D8" t="n">
-        <v>39.16513987714315</v>
+        <v>6.364335230035762</v>
       </c>
       <c r="E8" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F8" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.37210512814398</v>
+        <v>5.422967083323397</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16758746912029</v>
+        <v>5.552232963732048</v>
       </c>
       <c r="E9" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F9" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.96310131530766</v>
+        <v>2.594003963737495</v>
       </c>
       <c r="D10" t="n">
-        <v>16.32678805414992</v>
+        <v>2.653103058799361</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F10" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>53.206708036279</v>
+        <v>8.646090055895337</v>
       </c>
       <c r="D11" t="n">
-        <v>53.47084587274207</v>
+        <v>8.689012454320588</v>
       </c>
       <c r="E11" t="n">
-        <v>10.22376230125405</v>
+        <v>1.661361373953783</v>
       </c>
       <c r="F11" t="n">
-        <v>10.0565707089316</v>
+        <v>1.634192740201385</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
